--- a/光伏配储项目/电价数据/2026/乐园站.xlsx
+++ b/光伏配储项目/电价数据/2026/乐园站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5507300000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.29417</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.66711</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9781299999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.8237100000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.66522</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.46012</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.47489</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42997</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.47848</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40885</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.44385</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42926</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.43059</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42107</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.46551</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.54928</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.7217</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.58957</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.58836</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.25412</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.62249</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.6429400000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.8261799999999999</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.78887</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.8763500000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.70428</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.5822000000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.46618</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.73986</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.7818099999999999</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.14421</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.48557</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.6428700000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.6491399999999999</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.6596599999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.77195</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.75063</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.91238</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.13757</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7312000000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.54769</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.42243</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.66569</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.00385</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.04013</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.05263</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.10129</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.87298</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.07877</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.69706</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.36495</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.14015</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.12599</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.62576</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.27378</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.23117</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.15484</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.73572</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4792</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42181</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.05578</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.99499</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.14679</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53626</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226799999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50628</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49565</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50559</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47986</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5818</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.84561</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.73126</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.48052</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.81049</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.03911</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.66334</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.06585</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.9321200000000001</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.82138</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.6176699999999999</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.51162</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.51275</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.59102</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.9400599999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.0705</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.28753</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.9847</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.44188</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.01301</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.6899299999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.12248</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.97956</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.21888</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.60066</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.57202</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.59693</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.9309299999999999</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.00869</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.02205</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.02298</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.81421</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.20545</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.21897</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.63642</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.99233</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.1948</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.9623400000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.2509</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10609</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.72194</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.00351</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.52327</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.25289</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.68243</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7692899999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9209400000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33339</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5210499999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5302</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5750700000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.46219</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.47699</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39475</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.46112</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47982</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45444</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45103</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.62315</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.78891</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.0512</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.83645</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.64127</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.65163</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.58094</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64952</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.6524</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.07094</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.3392</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.58499</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.04484</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.38681</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.15006</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.00635</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.71738</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.77795</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.9917100000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.9993200000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8174400000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.54179</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.6481</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.05743</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.91271</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.00146</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.17177</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.01842</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.01308</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.17971</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.1862</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.18362</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.15708</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.18289</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.54862</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.9637</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.98861</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.47377</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.8920800000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.65631</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.96266</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9835199999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.9695900000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.0429</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.04228</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.08911</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.86039</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.6811900000000001</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.63401</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34315</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.94208</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5516799999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.58846</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.5139</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.52481</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.7202000000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.7591</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47871</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.44018</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.62566</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.6895</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.88864</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.03607</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.7221799999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.41058</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.63512</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.85942</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.72588</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.04387</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.40419</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.74193</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.79348</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.00425</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.5943200000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.14154</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.48469</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.58092</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.8582000000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.98746</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.17039</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.02504</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.8793800000000001</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.8249500000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.98162</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.94557</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.04551</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.27314</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.69445</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.19043</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.7622100000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.92316</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.04124</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.06252</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.98997</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.10934</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.18681</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.9908899999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.12853</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.62103</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.1121</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.15896</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18556</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.05896</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.00766</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.99237</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.9722499999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.11161</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.63581</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.48138</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.6293800000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31992</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7139099999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.46533</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.44541</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.47365</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.48808</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.6605</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.78216</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.56635</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.6467999999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.6700499999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.77971</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.64991</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.50604</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.49546</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.26189</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.22399</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.18695</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.21053</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5208700000000001</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.45988</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.55602</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.44209</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.44092</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.5280900000000001</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.46851</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.47558</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.46065</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34205</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.06092</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.8238099999999999</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.84296</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.54831</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.53406</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06612999999999999</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04304</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04385</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.0418</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.03940999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.26133</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.07718000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.26851</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.11719</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04721</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.00013</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04896</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.2795899999999999</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.18178</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.18999</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.19612</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.19853</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.43336</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.40319</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33322</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.43306</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.23014</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.25839</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.25185</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.23582</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.6352000000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.74837</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.5856699999999999</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.5592</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.5839099999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.65743</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.8131</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.46486</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.6534500000000001</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.6494099999999999</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.7705299999999999</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.5302100000000001</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.47936</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.47022</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.41326</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.04528</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.27302</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.66873</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.62546</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.56476</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.55043</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48026</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.6754199999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.77778</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7440800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.5522100000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.6831199999999999</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.9588300000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.28936</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.3087</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.06656</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.72664</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.67976</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.26125</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.95166</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.65242</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.28115</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.66004</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.34455</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7149800000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79743</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78767</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7826799999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87725</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.4992</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40789</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45697</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63935</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5404</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50717</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44842</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.46082</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42902</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45795</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5990800000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.55843</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6627000000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.0874</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.5971799999999999</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.47293</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5336799999999999</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.60738</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.96372</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.32286</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.28608</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.28266</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5503899999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8086100000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.55667</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.6249199999999999</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.5142899999999999</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.80363</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.72656</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.67755</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.59939</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5374800000000001</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.83731</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.70413</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.43597</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.56236</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.48824</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.54076</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.5232100000000001</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.55145</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.50625</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.52342</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.54913</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.45915</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.51189</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.5422899999999999</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.54615</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.48134</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.5384800000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.5624600000000001</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.6528099999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.64444</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.56399</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.55864</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.5679099999999999</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.5477300000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.5349400000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.53167</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.4669700000000001</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47886</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.4603</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.40088</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.36046</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95604</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47802</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5193099999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.53706</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.42049</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.56045</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.6227</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.73695</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.91839</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.88809</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.47279</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.05576</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.73025</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.82335</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.73754</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.57275</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.6909</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.9289500000000001</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.46822</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.7404400000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.6833</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.76709</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.03398</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.97948</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.67231</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.5671</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.6584</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.64311</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2546</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.23915</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.46164</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49445</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.17565</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.48776</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7035800000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7953300000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.74524</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.65104</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.05156</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.85881</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.57425</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.45249</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.63298</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.44613</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.24618</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.76356</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.10148</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.50576</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.84672</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.47042</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.35115</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.16497</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.09458</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.06152</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.9212400000000001</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.83239</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.59906</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.41236</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.23755</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.53547</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.79641</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.39812</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.68587</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.97864</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.97263</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.9203600000000001</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.8728899999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.11447</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.01115</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.74063</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.01815</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.49878</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.84545</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.89662</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.01478</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.82262</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.85991</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.47576</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.8022400000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.86142</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.9704400000000001</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.76367</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.75129</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.68457</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.9672000000000001</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.29101</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.83809</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.84138</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.67275</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32515</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.44221</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.41361</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8207000000000001</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.70017</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.43751</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.45105</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.44007</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.45479</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6450499999999999</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45538</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45538</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54396</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5328999999999999</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26658</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.45483</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.47588</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.68128</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.5893999999999999</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.63286</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8581299999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.28808</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.18102</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8611799999999999</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45251</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7072200000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.95037</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.18195</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.1345</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.03208</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54503</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43979</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49801</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41873</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.55092</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.7364400000000001</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.40734</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.95845</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.94396</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.93268</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9340599999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.58674</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.52386</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9577599999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.09849</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.74933</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.02553</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.7333</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.61398</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.60672</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.81463</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.31666</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.77373</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.37194</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.48889</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.10218</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.9255399999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.60623</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.58943</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.62312</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.63649</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.63155</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.60849</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.63299</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20752</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.66588</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.74777</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.66326</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.67105</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.67921</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.60169</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.71351</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.0341</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.1457</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.6571</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.66555</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.6593</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.73897</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.68912</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.77962</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6424099999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.45394</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.70636</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.86038</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34084</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.48407</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.01831</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.71635</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49343</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.49733</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.50441</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28437</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.44629</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.88793</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.43655</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.13473</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.91184</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7707000000000001</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50143</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4855</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44184</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48179</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34928</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.43949</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.71597</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.41832</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.50138</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.58355</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.48387</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5669</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42037</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.44727</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.64302</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.44542</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43031</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65178</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83175</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47215</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44102</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.55298</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76934</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.77695</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.4661</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.55824</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50498</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.73805</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.77238</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.56032</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50576</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45415</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.03273</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.51073</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.46602</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.11194</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.1435</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.10146</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.12026</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.13591</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.02502</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.20103</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14927</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13973</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.16813</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.83927</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19494</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.85034</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34648</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9155399999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.76647</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.95885</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.7425700000000001</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.22239</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.56125</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.1223</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7373099999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.18078</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.01315</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.42132</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.42272</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45347</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56528</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50349</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45365</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.55561</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46533</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.6398200000000001</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.65507</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.7816</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.64611</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.18651</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.25263</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.6017</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.53208</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.25045</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.9474900000000001</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.50173</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.45741</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.46477</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.49504</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.5406599999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.64888</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.06419</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.62151</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.78983</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.5900700000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.8108300000000001</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.7674</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.65557</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.62297</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.12813</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.12932</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.30784</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.10703</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.38991</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.63457</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.68487</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.99998</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.23208</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.91052</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.22532</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.99411</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48991</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.48193</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.9204</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.56072</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45796</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46101</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43775</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.46038</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.49499</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5185599999999999</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.80862</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.59515</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.57068</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.53102</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.98577</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.65389</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.7654500000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.89577</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.04049</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49613</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.16244</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54267</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.12617</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55338</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57594</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.47768</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23277</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.43111</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.46161</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.47251</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51274</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46136</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.48868</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.55133</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36412</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.73419</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.07293</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.56721</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.45656</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.43598</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.43826</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.53404</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.44778</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.45466</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.50487</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.42706</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41449</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.45992</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35286</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.7259500000000001</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22758</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23795</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.27623</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.27764</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.52036</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.02336</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.23859</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.19816</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.63528</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.51488</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.19825</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.7712100000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.45444</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.45416</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.04531</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.27188</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.6115900000000001</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.62048</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.71584</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.7091799999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.49478</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.37458</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.5284800000000001</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.41322</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.44958</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.7639900000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.43983</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7173200000000001</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.49052</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.1322</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.13563</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.08965</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.93359</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.80003</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.12937</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.49092</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.50945</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.45969</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.53565</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.6964600000000001</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5220399999999999</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5012799999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.10667</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.6963200000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.70009</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.52861</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.85256</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.69794</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.57092</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.69926</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.02094</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.5620599999999999</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.6130800000000001</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.55138</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.08663</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.74007</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.7308300000000001</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.75703</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.7757000000000001</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.03974</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.58051</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.79832</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.81894</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.43204</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.44687</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.62072</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.43252</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.60077</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.76356</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.14568</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.9820099999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.85326</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8809900000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.35203</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.2262</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.9970800000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40383</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.72376</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3438</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5425099999999999</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.7705</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.53477</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.72157</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7232000000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5428500000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.45906</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42052</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5754199999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.56352</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.52022</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5105500000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.43364</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.46791</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.54118</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.8006</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.03973</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.05138</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.96433</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.05404</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.61059</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.60538</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.97512</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.99358</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.5946699999999999</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55957</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5662</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25144</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5292</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5554199999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.51347</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.63315</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.4725</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.00006</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.6113200000000001</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5298099999999999</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.48427</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.46893</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.48497</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.48653</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.55698</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.54031</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.54271</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.48411</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.49866</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.54179</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.04184</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.9424600000000001</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.63802</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.56111</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.08122</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8262200000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.63595</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.02921</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.69372</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.46954</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.49738</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4855</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43392</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5200199999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34338</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.49714</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.46687</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.44658</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.42013</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.60515</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.55213</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.87748</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.97789</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.87741</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.84033</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.8961</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.8272</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.7886799999999999</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.81526</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.8040499999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.7812899999999999</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.7828999999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.54847</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.5257500000000001</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.56238</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.7917799999999999</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.97136</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.77956</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.9532200000000001</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.5596599999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.79531</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.7196900000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.7862899999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.50483</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.55154</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.57396</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.62261</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.68997</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.67276</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.74199</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.75443</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.73281</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.12926</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.00871</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.94731</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.26406</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.94389</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.04367</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.84527</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.6915399999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.69111</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.76625</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.62113</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69171</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.51004</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45853</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.66796</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.64679</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.61329</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.6821900000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6230800000000001</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.65428</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.4982200000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.48039</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.41882</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.85217</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.74648</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.8804299999999999</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.72576</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.88819</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.8710399999999999</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.87124</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.92537</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.9370700000000001</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.85541</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.09675</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.59257</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.45985</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.62798</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.62442</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.03787</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.58277</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.5922</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.71535</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.61284</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.7191</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.70083</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.73293</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.71816</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.6358</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.06699</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.05494</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.76001</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.19522</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.17091</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.9936200000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.77506</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.97057</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.12029</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.7754800000000001</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.16177</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.14119</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.49932</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.4152</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.1828</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.18461</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.78155</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.69233</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.7715299999999999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37512</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.72487</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.48845</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.82014</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.33106</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.01609</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9462699999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.97246</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.02369</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.15609</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.02371</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.87642</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6991499999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.15206</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.18526</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.18314</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.17124</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.88378</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.71569</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.1183</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.66436</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.12633</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.12624</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.14193</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.12426</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52664</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.21917</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.55963</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.5452400000000001</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15292</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.6531399999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.5907899999999999</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.20198</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.80959</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06715</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.91398</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.88478</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.02603</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.08131</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.14334</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.06278</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.07339</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.19178</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16903</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.19496</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.21215</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.12097</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.17888</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.02328</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.1322</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.11289</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.13946</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.18958</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.20785</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.18833</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.91635</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6016699999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.55884</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5214800000000001</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.51286</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37562</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.4632</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.32995</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.32586</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.74452</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.07985</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.46913</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5224800000000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84992</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.51973</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.60822</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.62407</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.57717</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.87379</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.68164</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.87913</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.09027</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.21203</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.32849</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.32126</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.47429</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.43759</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85472</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.47453</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7195900000000001</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7034400000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50893</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84717</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.79357</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.07839</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.76324</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5830700000000001</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.56021</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.55231</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.48452</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.6612899999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.53681</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.1289</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.11549</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.38155</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.11411</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.13533</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.13236</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.9995299999999999</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.97642</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.21029</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.00737</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.09457</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.94296</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.98366</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20973</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.96051</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.49625</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.7944</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80592</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56476</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.13337</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.85148</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5601</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55532</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56076</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.5160800000000001</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55477</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41961</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5219</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5017200000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.46019</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.46044</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43896</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49645</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.50017</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5496799999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5225299999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5220399999999999</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.56002</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.1796</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8857699999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49963</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.03483</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.51521</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.56726</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84254</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7934500000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59621</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85753</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.48481</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.53027</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.53528</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.18509</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55904</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.13789</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.55271</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55589</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58313</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.80243</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55959</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.80826</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.85205</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17861</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.80179</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68567</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.90283</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.15969</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.15012</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.14858</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8337100000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.7202499999999999</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6048</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.63979</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6455299999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.72072</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.84254</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.82496</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.58708</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.76789</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.72051</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.10515</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.68103</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.61181</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.57325</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.60384</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.60341</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.60742</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.63262</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6355499999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.75038</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70527</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60888</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5129900000000001</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40857</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
